--- a/Session_03/gradient_descent.xlsx
+++ b/Session_03/gradient_descent.xlsx
@@ -13,8 +13,8 @@
     <workbookView xWindow="45040" yWindow="-1820" windowWidth="30240" windowHeight="17260" xr2:uid="{63849087-0FE2-AF4B-ACB7-CB07C279593B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Gradient Desent" sheetId="1" r:id="rId1"/>
-    <sheet name="Gradient Desent (solved)" sheetId="2" r:id="rId2"/>
+    <sheet name="Gradient Descent" sheetId="1" r:id="rId1"/>
+    <sheet name="Gradient Descent (solved)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
